--- a/ci-cd-merge-resolver/repoCollector/datasets/serverless-java-container.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/serverless-java-container.xlsx
@@ -159,7 +159,7 @@
         <v>12</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>23.0</v>
+        <v>40.0</v>
       </c>
       <c r="E2" t="n" s="0">
         <v>2.0</v>
@@ -174,10 +174,10 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>0.046000003814697266</v>
+        <v>0.5130000114440918</v>
       </c>
       <c r="J2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -191,7 +191,7 @@
         <v>15</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>19.0</v>
+        <v>36.0</v>
       </c>
       <c r="E3" t="n" s="0">
         <v>2.0</v>
@@ -206,10 +206,10 @@
         <v>1</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>0.03999999910593033</v>
+        <v>0.5870000123977661</v>
       </c>
       <c r="J3" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -223,7 +223,7 @@
         <v>18</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>34.0</v>
+        <v>51.0</v>
       </c>
       <c r="E4" t="n" s="0">
         <v>4.0</v>
@@ -238,10 +238,10 @@
         <v>1</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>0.04699999839067459</v>
+        <v>0.5419999957084656</v>
       </c>
       <c r="J4" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
